--- a/tables/Table_S1_meta.xlsx
+++ b/tables/Table_S1_meta.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cong/Documents/GitHub/Taiji_ALTRA/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garysfiresteinmd/Library/CloudStorage/Dropbox/Mac (4)/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE176FA-914C-5943-9E5B-34EDB559C129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679CBB34-721B-AC45-B6C5-01B6C14F4BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{D95885FD-83F9-E74C-8A85-888C1A1B67E2}"/>
+    <workbookView xWindow="-60" yWindow="600" windowWidth="42620" windowHeight="24680" xr2:uid="{D95885FD-83F9-E74C-8A85-888C1A1B67E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="67">
   <si>
     <r>
       <t xml:space="preserve">Supplementary Table S1. </t>
@@ -160,9 +160,6 @@
     <t>not applicable</t>
   </si>
   <si>
-    <t>3 on  MTX (50%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">C-reactive protein, median mg/L (IQR) </t>
   </si>
   <si>
@@ -185,6 +182,87 @@
   </si>
   <si>
     <t>20 (10.75-25.5)</t>
+  </si>
+  <si>
+    <t>2 (0-6)</t>
+  </si>
+  <si>
+    <t>76 (39.8-183)</t>
+  </si>
+  <si>
+    <t>262 (262)</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serum RF IgA, median (IQR) </t>
+  </si>
+  <si>
+    <t>0 (0-0.32)</t>
+  </si>
+  <si>
+    <t>0.25 (0.25-4.63)</t>
+  </si>
+  <si>
+    <t>12.87 (2.72-29,6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serum RF IgM, median (IQR) </t>
+  </si>
+  <si>
+    <t>2.12 (0-7.7)</t>
+  </si>
+  <si>
+    <t>0.25 (0.25-3.65)</t>
+  </si>
+  <si>
+    <t>87.06 (55.78-104.75)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>One Control had a low titer CCP3 (1.3x ULN) and was also evaluated CCP3.1 (1.0x ULN). This asymptomatic individual did not meet entry criteria for the at-risk population</t>
+    </r>
+  </si>
+  <si>
+    <t>established RA</t>
+  </si>
+  <si>
+    <t>4 (80%)</t>
+  </si>
+  <si>
+    <t>53 (11)</t>
+  </si>
+  <si>
+    <t>16 (13-19)</t>
+  </si>
+  <si>
+    <t>not available</t>
+  </si>
+  <si>
+    <t>Cohort</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>Validation</t>
   </si>
   <si>
     <r>
@@ -207,64 +285,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, median (IQR) </t>
-    </r>
-  </si>
-  <si>
-    <t>2 (0-6)</t>
-  </si>
-  <si>
-    <t>76 (39.8-183)</t>
-  </si>
-  <si>
-    <t>262 (262)</t>
-  </si>
-  <si>
-    <t>&lt;0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serum RF IgA, median (IQR) </t>
-  </si>
-  <si>
-    <t>0 (0-0.32)</t>
-  </si>
-  <si>
-    <t>0.25 (0.25-4.63)</t>
-  </si>
-  <si>
-    <t>12.87 (2.72-29,6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serum RF IgM, median (IQR) </t>
-  </si>
-  <si>
-    <t>2.12 (0-7.7)</t>
-  </si>
-  <si>
-    <t>0.25 (0.25-3.65)</t>
-  </si>
-  <si>
-    <t>87.06 (55.78-104.75)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>One Control had a low titer CCP3 (1.3x ULN) and was also evaluated CCP3.1 (1.0x ULN). This asymptomatic individual did not meet entry criteria for the at-risk population</t>
+      <t>, median (IQR)(CCP2 for established RA)</t>
     </r>
   </si>
   <si>
@@ -287,17 +308,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> values for continuous variables were calculated using the two-sample Wilcoxon rank-sum test. P values for categorical variables were calculated using Fisher's exact test. BMI, body mass index; MTX, methotrexate; IQR, interquartile range; RF, rheumatoid factor; SD, standard deviation   </t>
+      <t xml:space="preserve"> values for continuous variables were calculated using the two-sample Wilcoxon rank-sum test. P values for categorical variables were calculated using Fisher's exact test. BMI, body mass index; MTX, methotrexate; TNF, Tumor Necrosis Factor Inhibitors; HCQ, Hydroxychloroquine; JAKi, Janus kinase inhibitor; IQR, interquartile range; RF, rheumatoid factor; SD, standard deviation   </t>
     </r>
   </si>
   <si>
-    <t>established RA</t>
-  </si>
-  <si>
-    <t>4 (80%)</t>
-  </si>
-  <si>
-    <t>53 (11)</t>
+    <t>3 TNF, 1  HCQ, 1  JAKi</t>
+  </si>
+  <si>
+    <t>4/5 above ULN</t>
+  </si>
+  <si>
+    <t>2/4 above ULN</t>
+  </si>
+  <si>
+    <t>3 (60%)</t>
+  </si>
+  <si>
+    <t>Established RA data derived  from clinical laboratories with upper limit of normal (ULN) RF &lt;10 IU/ml , CRP &lt;0/3 mg/dL</t>
+  </si>
+  <si>
+    <t>3  MTX (50%)</t>
   </si>
 </sst>
 </file>
@@ -343,49 +373,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -403,45 +396,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,6 +440,304 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -498,86 +767,9 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -600,187 +792,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -799,8 +810,9 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{F9D70B41-EB92-5048-911B-B001CA62521A}"/>
+    <tableStyle name="Table Style 2" pivot="0" count="0" xr9:uid="{C7FD9D5B-0E0A-1E4D-80C5-D14B934E0877}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -814,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB3BD01-3FFD-D848-B500-5F8E48B83A4B}" name="Table1" displayName="Table1" ref="A3:H15" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A3:H15" xr:uid="{20660585-0816-7B4F-BC5A-90C90A2E7D2E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8EB3BD01-3FFD-D848-B500-5F8E48B83A4B}" name="Table1" displayName="Table1" ref="A4:H16" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A4:H16" xr:uid="{20660585-0816-7B4F-BC5A-90C90A2E7D2E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{5193E210-7668-BE4C-8D94-9A6AA7E00BDF}" name="Group" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{CB5E5C51-E0DB-5948-A5FD-1A0092D40CD4}" name="CON" dataDxfId="6"/>
@@ -1147,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25DEE912-A590-2F44-8760-AA6588B1961F}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -1155,6 +1167,9 @@
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
     <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1163,351 +1178,376 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>35</v>
+      </c>
+      <c r="C5" s="2">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.154</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.50600000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.14799999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.59</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.308</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.19400000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5">
-        <v>35</v>
-      </c>
-      <c r="C4" s="5">
-        <v>26</v>
-      </c>
-      <c r="D4" s="5">
-        <v>6</v>
-      </c>
-      <c r="E4" s="8">
-        <v>5</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.154</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0.50600000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="F13" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="H13" s="2">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0.14799999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="F15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="2">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1.7999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.308</v>
-      </c>
-      <c r="H9" s="7">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.41399999999999998</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0.46400000000000002</v>
-      </c>
-      <c r="H11" s="7">
-        <v>0.19400000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="7">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0.46700000000000003</v>
-      </c>
-      <c r="H12" s="7">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="H15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="7">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="7">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="D16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="E16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.379</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0.379</v>
-      </c>
-      <c r="G15" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>53</v>
+    </row>
+    <row r="19" spans="1:1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">

--- a/tables/Table_S1_meta.xlsx
+++ b/tables/Table_S1_meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garysfiresteinmd/Library/CloudStorage/Dropbox/Mac (4)/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679CBB34-721B-AC45-B6C5-01B6C14F4BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9538CF-4917-6C48-9AB6-46B23A2685F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="600" windowWidth="42620" windowHeight="24680" xr2:uid="{D95885FD-83F9-E74C-8A85-888C1A1B67E2}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="42620" windowHeight="24680" xr2:uid="{D95885FD-83F9-E74C-8A85-888C1A1B67E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S1" sheetId="1" r:id="rId1"/>
@@ -289,6 +289,24 @@
     </r>
   </si>
   <si>
+    <t>4/5 above ULN</t>
+  </si>
+  <si>
+    <t>2/4 above ULN</t>
+  </si>
+  <si>
+    <t>3 (60%)</t>
+  </si>
+  <si>
+    <t>Established RA data derived  from clinical laboratories with upper limit of normal (ULN) RF &lt;10 IU/ml , CRP &lt;0/3 mg/dL</t>
+  </si>
+  <si>
+    <t>3  MTX (50%)</t>
+  </si>
+  <si>
+    <t>3 TNF, 1  HCQ, 1  JAKi, 2 Pred</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i/>
@@ -308,26 +326,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> values for continuous variables were calculated using the two-sample Wilcoxon rank-sum test. P values for categorical variables were calculated using Fisher's exact test. BMI, body mass index; MTX, methotrexate; TNF, Tumor Necrosis Factor Inhibitors; HCQ, Hydroxychloroquine; JAKi, Janus kinase inhibitor; IQR, interquartile range; RF, rheumatoid factor; SD, standard deviation   </t>
+      <t xml:space="preserve"> values for continuous variables were calculated using the two-sample Wilcoxon rank-sum test. P values for categorical variables were calculated using Fisher's exact test. BMI, body mass index; MTX, methotrexate; TNF, Tumor Necrosis Factor Inhibitors; HCQ, Hydroxychloroquine; JAKi, Janus kinase inhibitor; Pred, prednisone; IQR, interquartile range; RF, rheumatoid factor; SD, standard deviation   </t>
     </r>
-  </si>
-  <si>
-    <t>3 TNF, 1  HCQ, 1  JAKi</t>
-  </si>
-  <si>
-    <t>4/5 above ULN</t>
-  </si>
-  <si>
-    <t>2/4 above ULN</t>
-  </si>
-  <si>
-    <t>3 (60%)</t>
-  </si>
-  <si>
-    <t>Established RA data derived  from clinical laboratories with upper limit of normal (ULN) RF &lt;10 IU/ml , CRP &lt;0/3 mg/dL</t>
-  </si>
-  <si>
-    <t>3  MTX (50%)</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1166,7 @@
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="23.1640625" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -1311,7 +1311,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -1386,10 +1386,10 @@
         <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1409,7 +1409,7 @@
         <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2">
         <v>0.41399999999999998</v>
@@ -1461,7 +1461,7 @@
         <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>41</v>
@@ -1513,7 +1513,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F16" s="2">
         <v>0.379</v>
@@ -1535,12 +1535,12 @@
     </row>
     <row r="19" spans="1:1" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
